--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.29305726336614</v>
+        <v>5.410121805296997</v>
       </c>
       <c r="D2" t="n">
-        <v>40.54949003790074</v>
+        <v>6.58929213115887</v>
       </c>
       <c r="E2" t="n">
-        <v>3.683093445111901</v>
+        <v>0.5985026848306841</v>
       </c>
       <c r="F2" t="n">
-        <v>1.850602458941209</v>
+        <v>0.3007228995779462</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.55348602832039</v>
+        <v>7.077441479602064</v>
       </c>
       <c r="D3" t="n">
-        <v>42.20659313289621</v>
+        <v>6.858571384095634</v>
       </c>
       <c r="E3" t="n">
-        <v>3.683093445111901</v>
+        <v>0.5985026848306841</v>
       </c>
       <c r="F3" t="n">
-        <v>1.850602458941209</v>
+        <v>0.3007228995779462</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.77073293032664</v>
+        <v>6.300244101178079</v>
       </c>
       <c r="D4" t="n">
-        <v>41.69980975942465</v>
+        <v>6.776219085906506</v>
       </c>
       <c r="E4" t="n">
-        <v>3.683093445111901</v>
+        <v>0.5985026848306841</v>
       </c>
       <c r="F4" t="n">
-        <v>1.850602458941209</v>
+        <v>0.3007228995779462</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.10520511803326</v>
+        <v>6.029595831680405</v>
       </c>
       <c r="D5" t="n">
-        <v>37.44270782357507</v>
+        <v>6.084440021330949</v>
       </c>
       <c r="E5" t="n">
-        <v>3.683093445111901</v>
+        <v>0.5985026848306841</v>
       </c>
       <c r="F5" t="n">
-        <v>1.850602458941209</v>
+        <v>0.3007228995779462</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
